--- a/docs/qms/evidence-2026/19_Excel_Registers/EM26-20_Functional_Requirements.xlsx
+++ b/docs/qms/evidence-2026/19_Excel_Registers/EM26-20_Functional_Requirements.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Issued 2026-10-11 for review and approval</t>
+          <t>APPROVED — 2026-10-12 (AR-2026-003)</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -840,10 +840,14 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>To be confirmed</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr"/>
+          <t>Alexander Peter</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -858,10 +862,14 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>To be confirmed</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
+          <t>Sheryl Nazareth</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -876,10 +884,14 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>To be confirmed</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
+          <t>Anita Johan</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -890,44 +902,92 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Change</t>
-        </is>
-      </c>
+          <t>Approval record</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>docs/qms/records/approvals/2026-10-12_AR-2026-003_register_approval.md — review and approval confirmed by each role holder on 2026-10-12. Signatures are their typed names (SOP-01 §6).</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Richard Watson Stephen Amudha (Lead Engineer)</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>First issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Anita Johan (Managing Director)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Approved — AR-2026-003</t>
         </is>
       </c>
     </row>

--- a/docs/qms/evidence-2026/19_Excel_Registers/EM26-20_Functional_Requirements.xlsx
+++ b/docs/qms/evidence-2026/19_Excel_Registers/EM26-20_Functional_Requirements.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FR register'!$A$4:$L$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Traceability'!$A$4:$G$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FR register'!$A$4:$M$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Traceability'!$A$4:$H$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Requirement changes'!$A$4:$G$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C7" s="2" t="n"/>
@@ -597,7 +597,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C8" s="2" t="n"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>APPROVED — 2026-10-12 (AR-2026-003)</t>
+          <t>Rev 1.0 APPROVED 2026-10-12 (AR-2026-003); rev 1.1 issued 2026-10-12 — approval of the revision to be confirmed</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -729,7 +729,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Every functional requirement with source, priority, status, delivery and verification</t>
+          <t>Every functional requirement with source, priority, status, delivery, first version and verification</t>
         </is>
       </c>
       <c r="C18" s="2" t="n"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Requirement → review → delivery commit → test → release</t>
+          <t>Requirement → review → delivery commit → version → test → release</t>
         </is>
       </c>
       <c r="C19" s="2" t="n"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -840,14 +840,10 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Alexander Peter</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
+          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -862,14 +858,10 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Sheryl Nazareth</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
+          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -884,14 +876,10 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Anita Johan</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
+          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -912,7 +900,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>docs/qms/records/approvals/2026-10-12_AR-2026-003_register_approval.md — review and approval confirmed by each role holder on 2026-10-12. Signatures are their typed names (SOP-01 §6).</t>
+          <t>Rev 1.0: docs/qms/records/approvals/2026-10-12_AR-2026-003_register_approval.md — confirmed by each role holder on 2026-10-12. Rev 1.1 is signed here when they confirm it. Signatures are their typed names (SOP-01 §6).</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
@@ -988,6 +976,28 @@
       <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Approved — AR-2026-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha (Lead Engineer)</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Versions v1.0.0–v1.4.1 added (v1.0.0–v1.3.0 retrospective baselines, REG-08 §2a); version reviews</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1024,9 +1034,10 @@
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,7 +1050,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Priority: Must / Should / Could. Status from the commit record and the latest test run.</t>
+          <t>Priority: Must / Should / Could. ‘First version’ is the version (REG-08) that first contained the requirement; ‘Verified in’ the release whose tests verified it.</t>
         </is>
       </c>
     </row>
@@ -1091,17 +1102,22 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
+          <t>First version</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
           <t>Current implementation</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>Release</t>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>Verified in</t>
         </is>
       </c>
     </row>
@@ -1153,15 +1169,20 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
+          <t>2025 appliance</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
           <t>Carried into FR-KC-02 / FR-KC-03</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>2025 Test case 1 — UI loading and basic LLM query</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>2025 appliance</t>
         </is>
@@ -1215,15 +1236,20 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
+          <t>2025 appliance</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
           <t>Carried into FR-LT-01 / FR-LT-03</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>2025 Test case 2; TC-EM-Transcribe-003</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>2025 appliance</t>
         </is>
@@ -1277,15 +1303,20 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
+          <t>2025 appliance</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
           <t>Carried into FR-KC-01</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>TC-EM-UI-Upload-001</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>2025 appliance</t>
         </is>
@@ -1339,15 +1370,20 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
+          <t>2025 appliance</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
           <t>Carried into FR-PL-01 (Docker Compose)</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>TC-EM-Stacks-002</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>2025 appliance</t>
         </is>
@@ -1401,15 +1437,20 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
           <t>docs/USER_MANUAL.md / .pdf</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Document review</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -1463,15 +1504,20 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
           <t>Offline preparation 0818cdc; offline bundle scripts</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>TC-EM-OPS-105; Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -1525,15 +1571,20 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
           <t>Ingestion overhaul 7e582e1 (2026-08-16); allow-list e0ed4d0</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>TC-EM-DOC-102 — Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -1587,15 +1638,20 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
           <t>Honest citations 343117f (2026-07-29)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>TC-EM-RAG-103 — Pass (run 4, 2026-10-06); golden suite</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -1649,15 +1705,20 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
           <t>TensorRT-LLM streaming</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Unit tests (CI)</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -1711,15 +1772,20 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
           <t>Hierarchical section → chunk retrieval; BookRAG off (2decb99)</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>Golden suite 50/52 (2026-07-30)</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -1773,15 +1839,20 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
           <t>Persona types 518fb8e (04-08); per-vertical personas c6b834d (06-27)</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Manual check; persona quality overhaul 343117f</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -1835,15 +1906,20 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
           <t>Follow-up context b6aa963 (07-29)</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Golden suite multi-turn items</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -1897,15 +1973,20 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
           <t>Namespace predicate on all paths 4e27109 (08-07)</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>TC-EM-ISO-104 — Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -1959,15 +2040,20 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>Manual check</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -2021,15 +2107,20 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
           <t>Nemotron streaming ASR (d89aeda, 04-08)</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>TC-EM-TRN-112 — Not executed (run 4, 2026-10-06) — manual test outstanding</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -2083,15 +2174,20 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
           <t>Parakeet-TDT final, Nemotron partials</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>Voice end-to-end test 8e6d984; unit tests</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -2145,15 +2241,20 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
           <t>Auto-store every 60 s</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Unit tests</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -2207,15 +2308,20 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>Manual check</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -2269,15 +2375,20 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
           <t>Always-surface mode f75121b (06-27)</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>Unit tests; scenario harness</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -2331,15 +2442,20 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>Unit tests</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -2393,15 +2509,20 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
           <t>Gated checks 15f3c96 (09-14)</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>Scenario harness (silent-assistant v2)</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -2455,15 +2576,20 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
           <t>VibeVoice-ASR in an isolated process; Nemotron fallback</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>TC-EM-BRD-111 — Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="M26" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -2517,15 +2643,20 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
           <t>Report salvage 724fb98 (09-04)</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>TC-EM-BRD-111 — Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -2579,15 +2710,20 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
           <t>Speculative replies ff29843 (09-21)</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>Paper E4/E7 (2026-08-07); 12 spoken turns (09-21)</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="M28" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -2641,15 +2777,20 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
           <t>Tuned 5088c93 (06-26)</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>Paper E7: success 1.00; stop time 2.13 s (NFR-P07 open)</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -2703,15 +2844,20 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
           <t>Financial-assistant behaviour 95d3512 (03-08)</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>Manual check</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -2765,15 +2911,20 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
           <t>Piper default; Kokoro optional</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>Manual check</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -2827,15 +2978,20 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>TC-EM-DGEN-110 — Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -2889,15 +3045,20 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>TC-EM-DGEN-110 — Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -2951,15 +3112,20 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>Manual check (image status endpoint)</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -3013,15 +3179,20 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
           <t>18 built-in templates + custom upload</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>TC-EM-DGEN-110 — Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -3075,15 +3246,20 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
           <t>Logout revokes tokens e0ed4d0</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>TC-EM-AUTH-101 — Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -3137,15 +3313,20 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
           <t>Caller identified before the request 3feb5db</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>TC-EM-AUTH-101 — Pass (run 4, 2026-10-06) (AC-101.8)</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -3199,15 +3380,20 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
           <t>Key formats e0ed4d0</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>TC-EM-EXP-108 — Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -3261,15 +3447,20 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>Manual check</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -3323,15 +3514,20 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
           <t>Configuration not yet in the repository (AC-26)</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>Demonstrated on the unit; record to be added (AC-26)</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>Deployment unit</t>
         </is>
@@ -3385,15 +3581,20 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
           <t>Login enforced; checked every 6 h</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>External gate check (every 6 h)</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -3447,15 +3648,20 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
+          <t>v1.4.0</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
           <t>/api/version, voice /health, /build.json</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>TC-EM-REL-106 — Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -3509,22 +3715,27 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
+          <t>v1.4.0</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
           <t>Nightly off-host copy to be installed (R-02)</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>TC-EM-BKP-113 — Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L43"/>
+  <autoFilter ref="A4:M43"/>
   <printOptions gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -3545,16 +3756,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3587,17 +3799,22 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
+          <t>First version</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
           <t>Verification</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Release</t>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Verified in</t>
         </is>
       </c>
     </row>
@@ -3624,15 +3841,20 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>2025 appliance</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>2025 Test case 1</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>UI loading and basic LLM query</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>2025 appliance</t>
         </is>
@@ -3661,15 +3883,20 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>2025 appliance</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>2025 Test case 2; TC-EM-Transcribe-003</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>2025 appliance</t>
         </is>
@@ -3698,15 +3925,20 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>2025 appliance</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-UI-Upload-001</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>2025 appliance</t>
         </is>
@@ -3735,15 +3967,20 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>2025 appliance</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-Stacks-002</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>2025 appliance</t>
         </is>
@@ -3772,15 +4009,20 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Document review</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -3809,15 +4051,20 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-OPS-105; Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -3846,15 +4093,20 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-DOC-102</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -3883,15 +4135,20 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-RAG-103</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06); golden suite</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -3920,15 +4177,20 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Unit tests (CI)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -3957,15 +4219,20 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Golden suite 50/52 (2026-07-30)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -3994,15 +4261,20 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>Manual check; persona quality overhaul 343117f</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4031,15 +4303,20 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>Golden suite multi-turn items</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4068,15 +4345,20 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-ISO-104</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -4105,15 +4387,20 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>Manual check</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4142,15 +4429,20 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-TRN-112</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Not executed (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -4179,15 +4471,20 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Voice end-to-end test 8e6d984; unit tests</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4216,15 +4513,20 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>Unit tests</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4253,15 +4555,20 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Manual check</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4290,15 +4597,20 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>Unit tests; scenario harness</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4327,15 +4639,20 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>Unit tests</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4364,15 +4681,20 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>v1.3.0</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>Scenario harness (silent-assistant v2)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4401,15 +4723,20 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-BRD-111</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -4438,15 +4765,20 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-BRD-111</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -4475,15 +4807,20 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>Paper E4/E7 (2026-08-07); 12 spoken turns (09-21)</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4512,15 +4849,20 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>Paper E7: success 1.00; stop time 2.13 s (NFR-P07 open)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4549,15 +4891,20 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>Manual check</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4586,15 +4933,20 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>Manual check</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4623,15 +4975,20 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-DGEN-110</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -4660,15 +5017,20 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-DGEN-110</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -4697,15 +5059,20 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>Manual check (image status endpoint)</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4734,15 +5101,20 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-DGEN-110</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -4771,15 +5143,20 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-AUTH-101</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -4808,15 +5185,20 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-AUTH-101</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06) (AC-101.8)</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -4845,15 +5227,20 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-EXP-108</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -4882,15 +5269,20 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
           <t>Manual check</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
@@ -4919,15 +5311,20 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
           <t>Demonstrated on the unit; record to be added (AC-26)</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Deployment unit</t>
         </is>
@@ -4956,15 +5353,20 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
           <t>External gate check (every 6 h)</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>See verification</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -4993,15 +5395,20 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
+          <t>v1.4.0</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-REL-106</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>v1.4.1</t>
         </is>
@@ -5030,22 +5437,27 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
+          <t>v1.4.0</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
           <t>TC-EM-BKP-113</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>Pass (run 4, 2026-10-06)</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>v1.4.0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G43"/>
+  <autoFilter ref="A4:H43"/>
   <printOptions gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>

--- a/docs/qms/evidence-2026/19_Excel_Registers/EM26-20_Functional_Requirements.xlsx
+++ b/docs/qms/evidence-2026/19_Excel_Registers/EM26-20_Functional_Requirements.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0 APPROVED 2026-10-12 (AR-2026-003); rev 1.1 issued 2026-10-12 — approval of the revision to be confirmed</t>
+          <t>APPROVED — rev 1.1 2026-10-12 (AR-2026-004); rev 1.0 2026-10-12 (AR-2026-003)</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -840,10 +840,14 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr"/>
+          <t>Alexander Peter</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -858,10 +862,14 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
+          <t>Sheryl Nazareth</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -876,10 +884,14 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0 signed 2026-10-12; rev 1.1 to confirm</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr"/>
+          <t>Anita Johan</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -900,7 +912,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Rev 1.0: docs/qms/records/approvals/2026-10-12_AR-2026-003_register_approval.md — confirmed by each role holder on 2026-10-12. Rev 1.1 is signed here when they confirm it. Signatures are their typed names (SOP-01 §6).</t>
+          <t>Rev 1.1: docs/qms/records/approvals/2026-10-12_AR-2026-004_register_revision_approval.md; rev 1.0: …/2026-10-12_AR-2026-003_register_approval.md. Review and approval confirmed by each role holder; signatures are their typed names (SOP-01 §6).</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
@@ -998,6 +1010,28 @@
       <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Versions v1.0.0–v1.4.1 added (v1.0.0–v1.3.0 retrospective baselines, REG-08 §2a); version reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Anita Johan (Managing Director)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Approved — AR-2026-004</t>
         </is>
       </c>
     </row>
